--- a/DTY May26產銷260507-1400+500+30_clear.xlsx
+++ b/DTY May26產銷260507-1400+500+30_clear.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X95"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6624,242 +6624,6 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr"/>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="3" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr"/>
-      <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>FP82170R(L56&gt;82173R</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr"/>
-      <c r="O92" s="4" t="inlineStr"/>
-      <c r="P92" s="4" t="inlineStr"/>
-      <c r="Q92" s="4" t="inlineStr"/>
-      <c r="R92" s="4" t="inlineStr"/>
-      <c r="S92" s="4" t="inlineStr"/>
-      <c r="T92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="4" t="inlineStr"/>
-      <c r="W92" s="4" t="inlineStr"/>
-      <c r="X92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>FD2F41T2 like</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>AW1440kg JH</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>3SEC</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>75/72/2 SDFFR*</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>5/11-5/21X</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>FP81209R</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>120/72 SDR*</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N93" s="4" t="inlineStr"/>
-      <c r="O93" s="4" t="inlineStr"/>
-      <c r="P93" s="4" t="inlineStr"/>
-      <c r="Q93" s="4" t="inlineStr"/>
-      <c r="R93" s="4" t="inlineStr"/>
-      <c r="S93" s="4" t="inlineStr"/>
-      <c r="T93" s="4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U93" s="4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="V93" s="4" t="inlineStr"/>
-      <c r="W93" s="4" t="inlineStr"/>
-      <c r="X93" s="4" t="inlineStr">
-        <is>
-          <t>2F41T2 LIKE</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>FD2F25R2 like</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>AW504kg JH</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>3SEC</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>50/72/2 SDFFR*</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>5/11-5/16X</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>FP80099R</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>85/72 SDR*</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M94" s="4" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
-      <c r="P94" s="4" t="inlineStr"/>
-      <c r="Q94" s="4" t="inlineStr"/>
-      <c r="R94" s="4" t="inlineStr"/>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="4" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="U94" s="4" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="V94" s="4" t="inlineStr"/>
-      <c r="W94" s="4" t="inlineStr"/>
-      <c r="X94" s="4" t="inlineStr">
-        <is>
-          <t>2F25R2 LIKE</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr"/>
-      <c r="C95" s="4" t="inlineStr"/>
-      <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>FP80099R</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr"/>
-      <c r="K95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="4" t="inlineStr"/>
-      <c r="O95" s="4" t="inlineStr"/>
-      <c r="P95" s="4" t="inlineStr"/>
-      <c r="Q95" s="4" t="inlineStr"/>
-      <c r="R95" s="4" t="inlineStr"/>
-      <c r="S95" s="4" t="inlineStr"/>
-      <c r="T95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="4" t="inlineStr"/>
-      <c r="W95" s="4" t="inlineStr"/>
-      <c r="X95" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
